--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545453</v>
       </c>
       <c r="B2" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>2180</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -775,7 +780,7 @@
         <v>122545355</v>
       </c>
       <c r="B3" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545453</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122545355</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545453</v>
+        <v>122545355</v>
       </c>
       <c r="B2" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647025</v>
+        <v>647035</v>
       </c>
       <c r="R2" t="n">
-        <v>6545865</v>
+        <v>6545911</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545355</v>
+        <v>122545453</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647035</v>
+        <v>647025</v>
       </c>
       <c r="R3" t="n">
-        <v>6545911</v>
+        <v>6545865</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545355</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122545453</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545355</v>
+        <v>122545453</v>
       </c>
       <c r="B2" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647035</v>
+        <v>647025</v>
       </c>
       <c r="R2" t="n">
-        <v>6545911</v>
+        <v>6545865</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545453</v>
+        <v>122545355</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647025</v>
+        <v>647035</v>
       </c>
       <c r="R3" t="n">
-        <v>6545865</v>
+        <v>6545911</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545453</v>
+        <v>122545355</v>
       </c>
       <c r="B2" t="n">
         <v>95015</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647025</v>
+        <v>647035</v>
       </c>
       <c r="R2" t="n">
-        <v>6545865</v>
+        <v>6545911</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545355</v>
+        <v>122545453</v>
       </c>
       <c r="B3" t="n">
         <v>95015</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647035</v>
+        <v>647025</v>
       </c>
       <c r="R3" t="n">
-        <v>6545911</v>
+        <v>6545865</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545355</v>
+        <v>122545453</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647035</v>
+        <v>647025</v>
       </c>
       <c r="R2" t="n">
-        <v>6545911</v>
+        <v>6545865</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545453</v>
+        <v>122545355</v>
       </c>
       <c r="B3" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647025</v>
+        <v>647035</v>
       </c>
       <c r="R3" t="n">
-        <v>6545865</v>
+        <v>6545911</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545453</v>
+        <v>122545355</v>
       </c>
       <c r="B2" t="n">
         <v>95126</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647025</v>
+        <v>647035</v>
       </c>
       <c r="R2" t="n">
-        <v>6545865</v>
+        <v>6545911</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545355</v>
+        <v>122545453</v>
       </c>
       <c r="B3" t="n">
         <v>95126</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647035</v>
+        <v>647025</v>
       </c>
       <c r="R3" t="n">
-        <v>6545911</v>
+        <v>6545865</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 3462-2025 artfynd.xlsx
+++ b/artfynd/A 3462-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545355</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122545453</v>
       </c>
       <c r="B3" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
